--- a/output/浙江/浙江_battle3.xlsx
+++ b/output/浙江/浙江_battle3.xlsx
@@ -428,12 +428,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -442,7 +442,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,88 +508,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>万学远</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>上海交通大学210教研组党支部</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>书记</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>葛洪升</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>中共浙江省台州地委</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>工作队组长、调研室组长、土改工作队中队长、办公室秘书、调研科科长</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>正科级</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>高校教研组党支部书记级别不明确，无足够信息推断具体行政级别，应判难以判断。</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>95</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>台州地委为正厅级，内设调研科科长为正科级，LLM2正确。</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海市青年联合会</t>
+          <t>猫跳河六级电站指挥部</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>主席</t>
+          <t>指挥、党委书记</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>副厅级</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -597,105 +597,109 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J3" t="n">
         <v>85</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>上海市青年联合会为正厅级群众团体，主席通常对应正厅级。</t>
+          <t>猫跳河六级电站指挥部为临时性工程建设机构，原文仅提供职务而未说明机构隶属层级或对应行政级别，无法确定其正厅或副厅，信息不足定级。</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>万学远</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>中共浙江省委</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>100</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>省委副书记为标准副省部级，LLM1判断正确</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>葛洪升</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>浙江半山电厂指挥部</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>指挥、党委书记</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>半山电厂指挥部为省重点工程，指挥通常为副厅级；其前职系地厅级单位副职，平调为副厅级，后续升任正厅级省电力局局长，故副厅级更准确。</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>人事部</t>
+          <t>浙江省经委</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>副部长、党组副书记</t>
+          <t>副主任、党组副书记</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -710,36 +714,36 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>人事部为正部级单位，副部长为副部级</t>
+          <t>浙江省经委为正厅级单位，副主任为副厅级，LLM1判断正确；LLM2误将副主任定为正厅级。</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>国家外国专家局</t>
+          <t>国务院特区办公室</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>局长、党组书记</t>
+          <t>副主任、党组副书记</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -759,7 +763,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -768,42 +772,42 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>国家外国专家局是国务院部委管理的国家局，通常为副部级单位，局长对应副部级。</t>
+          <t>葛洪升原为浙江省省长（正部级），调任国务院特区办副主任时明确为正部长级，实际为正部级。</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>吕祖善</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南京航空学院</t>
+          <t>全国人大财经委员会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>留校待分配</t>
+          <t>副主任委员</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -818,46 +822,46 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>留校待分配属于毕业后等待分配，无实际职务，不具备行政级别，应为‘无’。</t>
+          <t>全国人大专门委员会副主任委员标准为副部级岗位，无明确正部长级标注时按基准定级，故LLM1更准确。</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>厦门市政府</t>
+          <t>中共中央委员会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>十三届中央候补委员</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -867,51 +871,55 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J8" t="n">
         <v>85</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>厦门为副省级市，市政府副秘书长通常为副厅级，LLM2判断更合理。</t>
+          <t>中央候补委员属于党内职务，本身不直接对应行政级别，且本条经历未提供同时担任的行政职务，无法推断具体级别。</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中共厦门市湖里区委</t>
+          <t>中共中央委员会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>十四届中央委员</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -921,51 +929,55 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J9" t="n">
         <v>95</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>厦门为副省级城市，区委副职为副厅级，LLM2正确</t>
+          <t>中央委员本身无固定行政级别，需结合当时具体职务判断，不能笼统判定为正部级或判定为无。</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>葛洪升</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>厦门市政府</t>
+          <t>全国人大常委会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>九届全国人大常委会委员</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,204 +996,204 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>厦门为副省级城市，市政府副秘书长通常为副厅级，LLM2判断符合惯例。</t>
+          <t>全国人大常委会委员通常对应正部级，LLM1判断为“无”明显错误。</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>葛洪升</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>电力工业部（水利电力部）新安江工程局</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>党委办公室副主任、党委宣传部副部长、部长</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>万学远</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上海交通大学210教研组党支部</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>书记</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>正科级</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>职务含副主任/副部长，级别不唯一，早期工程局级别不确定</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>85</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>高校教研组党支部书记多为兼职，无明确行政级别对应，无法用标准行政级别衡量，信息不足定级。</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>葛洪升</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>万学远</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>水利电力部新安江工程局党委宣传部</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>部长</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>水利电力部新安江工程局级别不明，党委宣传部部长定级依据不足，应填难以判断</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上海市青年联合会</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>主席</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>90</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>上海市为直辖市，市青年联合会作为地方性人民团体一般为正厅级，主席为正厅级正职。</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>葛洪升</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>水利电力部贵州水电建设公司党委</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>常委、政治部主任</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>单位级别不明确，仅凭职务无法确定级别，应遵循难以判断规则。</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>万学远</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>副部长、党组副书记</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>95</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>人事部为正部级国务院组成部门，副部长为副部级，党组副书记不改变行政级别。</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>万学远</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>猫跳河六级电站指挥部</t>
+          <t>国家外国专家局</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>指挥、党委书记</t>
+          <t>局长、党组书记</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1191,51 +1203,51 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>早期工程项目指挥部级别不明，仅凭单位名称无法定级，LLM2更稳妥。</t>
+          <t>国家外国专家局为人社部管理的副部级国家局，局长、党组书记应为副部级，LLM1判断正确，LLM2误作正部级。</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>万学远</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>浙江半山电厂指挥部</t>
+          <t>中国国际人才交流协会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>指挥、党委书记</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1248,52 +1260,48 @@
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>半山电厂指挥部级别不明确，无明确职级线索，难以推断具体级别。</t>
+          <t>万学远卸任国家外国专家局局长(明确正部长级)后任此职，保留正部级待遇，协会副主席按本人原级别定级。</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中共宁波市委</t>
+          <t>东北丰满水力发电厂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>学员</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1303,7 +1311,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1312,42 +1320,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1986-1988年宁波尚未成为副省级市，市委书记按地级市为正厅级。</t>
+          <t>学员非全日制学生,按早期模糊职务规则应填难以判断,LLM1误填为无</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>国务院特区办公室</t>
+          <t>浙江黄坛口水电厂</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>副主任、党组副书记</t>
+          <t>学员</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1357,51 +1365,51 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>国务院特区办公室属副部级机构，副主任为副部级，正部级判断过高</t>
+          <t>电厂学员属岗前培训，非全日制学生，亦无职务级别，难以判断行政级别。</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>全国人大财经委员会</t>
+          <t>新安江水电运行分场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>值班员、机械值班长、党支部书记</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1420,38 +1428,42 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>葛洪升曾任正部级省长/省委书记，全国人大财经委副主任委员由正部级干部担任属平级退居二线</t>
+          <t>值班员、机械值班长等职务无明确级别对应，信息不足。</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>富春江水电厂</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>离职休养</t>
+          <t>值班员、党支部书记、党委委员、揭批查办公室负责人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1461,25 +1473,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>仅凭'离职休养'无法推断级别，需结合此前职务，但无额外信息</t>
+          <t>富春江水电厂的企业级别不明，值班员、党支部书记等职务无法直接确定行政级别，信息不足以定级，故LLM2的“难以判断”更准确。</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -1490,21 +1498,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>东北丰满水力发电厂</t>
+          <t>富春江水电厂</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>学员</t>
+          <t>党委常委、副书记、厂长、党委书记</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1519,21 +1527,21 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>学员为学习经历，无行政级别，LLM1正确</t>
+          <t>富春江水电厂行政级别未知，虽有厂长/党委书记职务，但无法从原文确定其处级/厅级归属，属难以判断。</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -1544,21 +1552,21 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>浙江黄坛口水电厂</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>学员</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1573,104 +1581,104 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
+        <v>95</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>仅凭‘中央党校 进修学员’无法确定班次与级别，需结合前后职务推断；孤立条目应标‘难以判断’。</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>张德江</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>朝鲜金日成综合大学经济系</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>进修学员</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>90</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>学员为非干部身份的学习经历，无行政级别，而非信息不足难以判断。</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>柴松岳</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>中共富春江水电厂委员会</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>常委、副书记、厂长、党委书记</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>仅凭电厂厂长职务无法确定级别，正处和副厅均可能</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>仅凭‘进修学员’无法判断是否在职进修或保留原级别，缺乏前后履历依据。</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>柴松岳</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中共延边州委</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1685,50 +1693,46 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>95</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>中央党校进修学员本身无行政级别，需结合原职务推断，原文无此信息。</t>
+          <t>延边州为地级行政区，州委为正厅级单位，副书记常规为副厅级，LLM2判断准确。</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>柴松岳</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>浙江省计划经济委员会</t>
+          <t>中共吉林省委</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>主任、党组书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1743,51 +1747,51 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>浙江省计划经济委员会为省级政府组成部门，主任为正厅级</t>
+          <t>省委专职副书记（非省长）标准级别为副部级，LLM2判断正确。LLM1误判为正部级。</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>柴松岳</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共延边州委</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1806,19 +1810,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>省委副书记是省级副职，标准副部级，无证据显示高配正部级。</t>
+          <t>延边州为地级自治州，非副省级城市，其党委书记标配正厅级，除非明确省委常委兼任才会高配副部级，原文仅书记职务无高配信息，故正厅级更准确。</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1826,22 +1830,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>吉林省汪清县罗子沟公社太平大队</t>
+          <t>陕西省延川县文安驿公社梁家河大队</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>知青</t>
+          <t>知青、党支部书记</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>正科级</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>无</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1856,23 +1860,23 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>知青经历非干部职务，无行政级别，应填'无'而非'难以判断'。</t>
+          <t>大队党支部书记是村级职务，不纳入国家行政编制，无明确行政级别，符合'难以判断'规则。</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1880,17 +1884,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中共吉林省委</t>
+          <t>中共福州市委</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1905,28 +1909,28 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>省委副书记是副部级，LLM2正确</t>
+          <t>福州市为地级市（非副省级市），市委书记标准级别为正厅级；未提省委常委兼任，不能默认高配副部级。</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1934,12 +1938,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中共延边州委</t>
+          <t>福州市人大常委会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1964,46 +1968,46 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>延边州为地级行政区，州委书记常规为正厅级，无副部级高配依据。</t>
+          <t>福州市为普通地级市，非副省级市；福州市人大常委会主任为该市四大班子正职之一，职务本身为正厅级。</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中共广东省委</t>
+          <t>中共福州军分区党委</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>党委第一书记</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2013,7 +2017,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -2022,32 +2026,32 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>张德江任广东省委书记期间已任中央政治局委员，属副国级</t>
+          <t>福州市为地级市，福州市委书记为正厅级，兼任军分区党委第一书记不提升级别。</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>中共重庆市委</t>
+          <t>中共福建省委</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2057,7 +2061,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2072,46 +2076,46 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>重庆为直辖市，市委书记通常由中央政治局委员兼任，副国级</t>
+          <t>省委副书记为副部级，非省长兼任时无正部级依据。</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>张德江</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>国务院</t>
+          <t>中共福建省委、中共福州市委</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>副总理、党组成员</t>
+          <t>副书记、书记</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2121,21 +2125,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>国务院副总理是法定的副国级职务，LLM2判断正国级明显错误</t>
+          <t>福建省委副书记为副部级，兼任福州市委书记（正厅级），就高为副部级，非正部级。</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2146,16 +2150,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>中共福建省委</t>
+          <t>福州市人大常委会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2175,75 +2179,83 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>省委副书记为省部级副职，标准副部级，LLM1正部级错误</t>
+          <t>福州市为地级市，其人大常委会主任为正厅级，非副省级或正部级。</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>习近平</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>中共福州市委</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>书记</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="B33" t="n">
+        <v>22</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>福州军分区</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>党委第一书记</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>福州市为地级市但通常由省委常委兼任，市委书记一般为副部级，正部级明显错误。</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>90</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>仅凭“福州军分区党委第一书记”无法确定行政级别，两人判断均缺乏依据且明显错误。</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2254,16 +2266,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>福州市人大常委会</t>
+          <t>中共福建省委</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2283,25 +2295,21 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>95</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>福州市为地级市，市人大常委会主任标准为正厅级，两个判断均错误。</t>
+          <t>省委副书记一般为副部级，仅当兼任省长时为正部级，此处未注明兼任省长，故应为副部级</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2320,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>中共福建省福州市委</t>
+          <t>福建省高炮预备役师</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>党委第一书记</t>
+          <t>第一政委</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2346,20 +2354,20 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>福州市为地级市，市委第一书记为正厅级，两LLM均误判</t>
+          <t>预备役师第一政委通常由地方领导兼任，级别不确定，无法从职务本身判断。</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2378,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2404,16 +2412,16 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>省委副书记是副省级职务，对应副部级</t>
+          <t>单任省委副书记（未兼省长）为副部级，LLM1误判为正部级，LLM2判断正确。</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2424,26 +2432,26 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>福建省高炮预备役师</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>第一政委</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2453,25 +2461,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
         <v>95</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>预备役师第一政委为兼职，无固定级别，无法从单位+职务推断</t>
+          <t>国家副主席法定级别为国家级副职（副国级），不因个人党内兼任而改变该职务的基准级别。</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2482,26 +2486,26 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>中共福建省委</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2520,66 +2524,70 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>省委副书记为标准副部级职务，LLM2判断正确。</t>
+          <t>国家副主席职务基准为副国级；虽习近平当时高配正国级，但基于职务本身判断应取副国级。</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>习近平</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>50</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>中共中央政治局</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>常委</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="B39" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>中共中央军事委员会</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>副主席</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>正国级</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>100</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>中共中央政治局常委为正国级，LLM2判断正确。</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>中央军委副主席可为副国级或正国级（政治局常委兼任），单凭职务无法确定个人级别，需看是否政治局常委。</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2590,16 +2598,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>中共中央书记处</t>
+          <t>中华人民共和国中央军事委员会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2628,12 +2636,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>中共中央书记处书记职务本身为副国级，LLM1正确，LLM2可能混淆了个人整体级别。</t>
+          <t>中央军委副主席职务法定为副国级，正国级须主席职务。</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2644,16 +2652,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>校长</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2673,21 +2681,21 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>中央党校校长通常由正国级领导人兼任，习近平当时已担任正国级职务。</t>
+          <t>国家副主席职务本身为副国级，不考虑其兼任的其他更高职务。</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -2698,16 +2706,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>中共中央政治局</t>
+          <t>中华人民共和国中央军事委员会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2727,51 +2735,51 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>中共中央政治局常委属于正国级，非副国级。</t>
+          <t>中央军委副主席职务本身为副国级，不附加政治局常委等兼任信息时应按职务定级。</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>吕祖善</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>中共中央书记处</t>
+          <t>全国人大财政经济委员会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副主任委员</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2781,51 +2789,51 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>中共中央书记处书记基准为副国级，非正国级</t>
+          <t>吕祖善曾任浙江省省长（正部级），转任全国人大财经委副主任委员后保留原级别，实际为正部级。</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>吕祖善</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>中华人民共和国</t>
+          <t>第十二届全国人大常委会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>副主席</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2835,51 +2843,51 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>中华人民共和国副主席是副国级职务，而非正国级。</t>
+          <t>全国人大常委会委员（常委）通常享受正部级政治、生活待遇，惯例按正部级对待。</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>吕祖善</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>第十二届全国人大财政经济委员会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>校长</t>
+          <t>副主任委员</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2894,46 +2902,46 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>习近平任校长时已是正国级政治局常委，职务级别应随实际兼任者级别。</t>
+          <t>全国人大专门委员会副主任委员通常对应正部级，且吕祖善此前为浙江省省长（正部级），转任为平级调整。</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>中共中央政治局</t>
+          <t>中共内蒙古自治区呼伦贝尔盟牧管局党委</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>常委、政治部主任</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2943,51 +2951,51 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>中共中央政治局常委是正国级职务，LLM2正确。</t>
+          <t>牧管局级别不明，赵洪祝早期经历信息不足以确定具体级别，符合难以判断规则</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>中共中央书记处</t>
+          <t>中共内蒙古自治区扎兰屯牧场党委</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>常委、副书记、纪委书记</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>副科级</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3002,46 +3010,46 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>中共中央书记处书记一般为副国级，正国级是总书记特例。</t>
+          <t>扎兰屯牧场级别不明确，无法准确推断，故难以判断更合理。</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>中华人民共和国</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>副主席</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3051,105 +3059,109 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J48" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>国家副主席为副国级，符合宪法规定。</t>
+          <t>仅凭“中央党校 进修学员”无法确定级别，需此前职务，信息不足。</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>习近平</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>60</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>中共中央军事委员会</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>副主席</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>100</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>中共中央军事委员会副主席为副国级职务，LLM1判断正确。</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>赵洪祝</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>中共内蒙古自治区兴安盟委</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>委员</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>“中共兴安盟委 委员”未明确是否为常委，单独看无法确定级别，LLM1和LLM2均无充足依据。</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>中华人民共和国中央军事委员会</t>
+          <t>中共内蒙古自治区兴安盟委</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>副主席</t>
+          <t>委员、组织部部长</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3159,7 +3171,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -3168,23 +3180,23 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>中央军委副主席一般为副国级，习近平此时尚未担任国家主席。</t>
+          <t>兴安盟是地级行政区，盟委委员为副厅级，组织部长由盟委委员兼任，确为副厅级</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3193,17 +3205,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>校长</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>正国级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3213,105 +3225,109 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>90</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>仅“进修学员”无上下文，无法确定原级别，不符合“无”也不可妄定副厅，应判难以判断</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>夏宝龙</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>28</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>100</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>中央党校校长通常由正国级领导人兼任，习近平时任中央政治局常委正国级</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>赵洪祝</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>中共内蒙古自治区呼伦贝尔盟牧管局党委</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>常委、政治部主任</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>副处级</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>呼伦贝尔盟为地级行政区，牧管局通常为正处级单位，其党委常委相当于副处级，可以推断。</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>95</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>浙江省委副书记（非省长兼任）一般为专职副书记，属副部级。</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>中共内蒙古自治区扎兰屯牧场党委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>常委、副书记、纪委书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3326,46 +3342,46 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>扎兰屯牧场级别不明确，仅凭职务无法定级，应判难以判断。</t>
+          <t>省委副书记（不兼省长）标准级别为副部级，LLM2正确。</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中共浙江省委政法委员会</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3375,55 +3391,51 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>中央党校进修学员无明确级别，原职级未知，不宜直接定级为副处级或无。</t>
+          <t>浙江省委政法委书记通常由省委常委兼任，省委常委为副部级，该职务并非正部级。LLM1判断有误。</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>中共内蒙古自治区兴安盟委</t>
+          <t>浙江省社会治安综合治理委员会</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>委员</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3436,110 +3448,102 @@
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
+        <v>90</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>省级综治委主任通常由省委副书记兼任，为副部级，非正部级。</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>夏宝龙</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>32</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
         <v>100</v>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>兴安盟为地级行政区，盟委委员对应副厅级，LLM2正确。</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>赵洪祝</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>中央党校</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>进修学员</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>中央党校进修学员在职学习保留原级别，但单条经历无法确定级别，两者均无充分依据。</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>省委副书记（非省长）为副部级</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>中共内蒙古自治区兴安盟委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>委员、组织部部长</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3558,42 +3562,42 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>兴安盟为地级行政区，盟委委员、组织部部长通常为副厅级，LLM1正处级有误。</t>
+          <t>省委副书记通常为副部级，除非兼任省长才为正部级，此处仅副书记无兼任信息，应为副部级。</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>浙江省瑞安县莘塍区团委</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3603,55 +3607,51 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>90</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>仅凭'中央党校进修学员'无法判断具体级别，在职进修保留原级别但原级别未知。</t>
+          <t>县辖区团委负责人职务模糊，单位层级不足以确定正科级，信息不足宜判断为难以判断。</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>中央纪委</t>
+          <t>浙江省民政厅</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>党组成员、人事处处长</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3670,42 +3670,42 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>中央纪委常委通常为正部级，LLM1副部级偏低。</t>
+          <t>省民政厅为正厅级单位，内设人事处为正处级，处长为正处级，党组成员不改变行政级别，仍为正处级。</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>中央纪律检查委员会</t>
+          <t>中共永康市委</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>中央纪委副书记通常为正部级，副国级仅限兼任政治局委员或书记处书记，故LLM1更准确</t>
+          <t>永康为县级市，市委书记常规为正处级。无高配信息时，LLM1判断更准确。</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>中央纪律检查委员会</t>
+          <t>浙江大学研究生课程进修班</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>研究生</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3769,46 +3769,50 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J61" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>中央纪委副书记（专职）通常为正部级，赵洪祝任职时未同时担任副国级职务。</t>
+          <t>研究生课程进修班为学习经历，无法从该条推断行政级别，需结合前后职务确定是脱产(无)还是在职保留级别。</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>中共天津市河西区委</t>
+          <t>永康市人大常委会</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3823,7 +3827,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3832,23 +3836,23 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>直辖市的区为厅级，区委副书记为副厅级，非正厅级。</t>
+          <t>永康为普通县级市，四套班子正职为正处级，人大常委会主任为正处级，非副厅级。</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3857,19 +3861,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>秘书长</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>正厅级</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -3877,32 +3881,32 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>浙江省委副书记属省级副职，标准副部级。LLM1正厅级错误。</t>
+          <t>省委秘书长通常由省委常委兼任，省委常委为副部级，故应采纳LLM1的副部级判断。</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3916,12 +3920,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3931,51 +3935,51 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>浙江省委副书记职务为副部级</t>
+          <t>浙江省委副书记通常为副部级，未注明正部长级，故LLM1判断准确。</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>安徽省合肥市中级人民法院</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>助理审判员、审判员、办公室秘书、副主任、刑一庭副庭长、庭长、院党组成员</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3990,46 +3994,46 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>省委副书记为副部级，LLM1正厅级错误。</t>
+          <t>合肥市中级法院为副厅级，庭长通常为副处级，院党组成员亦对应副处级，LLM2判断正确。</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>华东政法学院</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4039,51 +4043,55 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J66" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>省委副书记为标准副部级，LLM1正厅级错误</t>
+          <t>仅凭进修学员无法确定级别，需上下文。LLM1误判为无，LLM2可能基于先验知识。</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>国务院港澳事务办公室</t>
+          <t>安徽省合肥市公安局</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>主任、党组书记</t>
+          <t>局长、党委副书记、书记</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4093,51 +4101,51 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>国务院港澳办主任为正部级，非副国级。</t>
+          <t>合肥市为普通地级市，其公安局为正处级单位，局长除非明确由副市长兼任，否则默认为正处级，LLM2正确。</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>中央港澳工作办公室</t>
+          <t>中共合肥市委</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4150,155 +4158,155 @@
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
         <v>95</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>中央港澳工作办公室主任通常由副国级领导兼任，夏宝龙现任全国政协副主席确认为副国级。</t>
+          <t>合肥市为地级市，正厅级架构；市委副书记应为副厅级，正厅级通常为市委书记/市长。</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>夏宝龙</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>国务院港澳事务办公室</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>主任</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>车俊</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>中共合肥市委</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>国务院港澳办主任常规正部级，但夏宝龙兼任全国政协副主席为副国级，LLM2更准确</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>90</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>合肥为普通地级市，正厅级建制，市委副书记（非市长兼任）常规为副厅级，LLM2正确。</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>李强</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>5</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>浙江省瑞安县莘塍区团委</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>正科级</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>车俊</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>中央党校函授学院</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>进修学员</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
-        <v>85</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>早期县区团委'负责人'职务模糊，难以确定具体职级</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="J70" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>仅凭'中央党校函授学院进修学员'无法确定其当时所任职务，无法推断行政级别；LLM1误判为无，LLM2无依据猜测副厅级，均不准确。</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>浙江省民政厅</t>
+          <t>中共合肥市委</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>党组成员、人事处处长</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4318,46 +4326,46 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>党组成员通常为副厅级，兼任人事处处长不改变其副厅级级别，而非单纯正处级。</t>
+          <t>合肥是普通地级市，市委副书记通常为副厅级，LLM2判断正确，LLM1误认为正厅级</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>中共永康市委</t>
+          <t>中共河北省委</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4367,51 +4375,51 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>永康市为县级市，市委书记标准级别为正处级。</t>
+          <t>专职省委副书记为副部级，无兼任省长等正部级职务，LLM2判断正确</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>中共永康市委</t>
+          <t>中共河北省委</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4421,7 +4429,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -4430,42 +4438,42 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>县级市市委书记标准为正处级，无高配证据，LLM2错误</t>
+          <t>省委副书记（非省长）通常为副部级，LLM2判断正确。</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>永康市人大常委会</t>
+          <t>中共石家庄市委</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4475,51 +4483,55 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
       <c r="J74" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>县级市人大常委会为正处级单位，主任对应正处级。</t>
+          <t>石家庄为地级市，中共石家庄市委为正厅级机构，书记为正职，无省委常委等明确高配信息，故应为正厅级。LLM1正部级明显错误，LLM2副部级属于无依据高配。</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共新疆维吾尔自治区委；中共新疆生产建设兵团委员会</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>秘书长</t>
+          <t>副书记；党委书记、政委</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>正厅级</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4534,46 +4546,46 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>省委秘书长通常由省委常委兼任，为副部级</t>
+          <t>新疆兵团为正省部级单位，党委书记、政委为正部级；LLM2仅看自治区党委副书记定级副部级，忽略兵团主官高配属实。</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>需拆分提取：新疆生产建设兵团和中国新建集团公司</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>需拆分提取：党委书记、政委和董事长</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4588,74 +4600,70 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>省委副书记标准级别为副部级，正部级错误</t>
+          <t>新疆生产建设兵团为正部级建制，党委书记兼政委通常为正部级</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>车俊</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>安徽省合肥市中级人民法院</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>助理审判员、审判员、办公室秘书、副主任、刑一庭副庭长、庭长、院党组成员</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>正科级</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>院党组成员级别不明，地级市中院党组成员可正处或副处，原文未明确职务等级</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="B77" t="n">
+        <v>30</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>中国新建集团公司</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>董事长</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>95</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>中国新建集团公司为新疆生产建设兵团企业化名称，兵团政委兼董事长为正部级建制，车俊任该职时确为正部级。</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -4666,26 +4674,26 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>安徽省合肥市公安局</t>
+          <t>中共新疆维吾尔自治区委、中共新疆生产建设兵团委员会</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>副局长、党委副书记</t>
+          <t>副书记、党委书记、政委</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4695,21 +4703,21 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>合肥市为地级市，公安局是正处级单位，副局长通常为副处级，LLM2判断更准确。</t>
+          <t>新疆生产建设兵团为正省级单位，政委为正部级；兼任自治区党委副书记不影响主职级别，LLM1判断更准确。</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -4720,26 +4728,26 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>中共合肥市委</t>
+          <t>新疆生产建设兵团</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>党委书记、政委</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4749,21 +4757,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>合肥为地级市，市委副书记常规为副厅级，无高配信息。</t>
+          <t>新疆生产建设兵团为正省级建制，党委书记、政委为正部长级，LLM1正确。</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -4774,26 +4782,26 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>中共合肥市委</t>
+          <t>中国新建集团公司</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>董事长</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4803,21 +4811,21 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>合肥市为地级市，市委副书记通常为副厅级，LLM2判断正确。</t>
+          <t>新疆生产建设兵团对外称中国新建集团公司，兵团政委兼任董事长，通常明确为正部长级（高配），车俊任期内即为正部级。</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -4828,26 +4836,26 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>中共合肥市委</t>
+          <t>中央新疆工作协调小组</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>成员</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4857,21 +4865,21 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>地级市市委副书记标准为副厅级，LLM2判断正确</t>
+          <t>车俊时任新疆生产建设兵团政委（正部级），中央新疆工作协调小组为其兼职，级别依主职定正部级。</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -4882,26 +4890,26 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团</t>
+          <t>中共新疆维吾尔自治区委</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>党委书记、政委</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4916,70 +4924,70 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团为正部级单位，党委书记、政委为正部级。</t>
+          <t>省委副书记（非省长）标准为副部级</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>车俊</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>中国新建集团公司</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>董事长</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="B83" t="n">
+        <v>36</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>中国新建集团公司为新疆生产建设兵团下属企业，董事长通常按副部级设置，车俊虽兼任兵团政委正部级，但单独此职务以机构级别为准。</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>95</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>省委副书记（非省长）通常为副部级，LLM1判正部级无依据。</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -4990,11 +4998,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5004,14 +5012,14 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -5019,51 +5027,51 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>新疆自治区党委副书记为副部级，符合标准</t>
+          <t>省委副书记（未兼任省长）为副部级，非正部级，LLM2判断正确。</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团</t>
+          <t>航空航天工业部五院501部结构室</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>党委书记、政委</t>
+          <t>副主任</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副科级</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5073,7 +5081,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -5082,96 +5090,100 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>车俊从河北省委副书记（副部级）平调兵团政委，且后来升任浙江省长（正部级），故当时为副部级。</t>
+          <t>航空航天工业部五院（中国空间技术研究院）为正局级，其501部（总体部）为正处级，下设结构室为科级，副主任为副科级。</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>车俊</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>33</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>中国新建集团公司</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>董事长</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="n">
-        <v>90</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>车俊曾任新疆生产建设兵团政委（正部），兼任中国新建集团董事长，董事长级别对应正部级。</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>袁家军</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>中国航天工业总公司五院</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>院长助理、神舟一号飞船系统常务副总指挥</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>航天工业总公司五院为厅级单位,院长助理级别通常在正处与副厅间,原文无足够信息定级,故难以判断</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>中央新疆工作协调小组</t>
+          <t>北京航空航天大学</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>成员</t>
+          <t>博士研究生</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5186,46 +5198,46 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>车俊当时任新疆自治区党委副书记兼兵团政委，为副部级；协调小组成员属兼职，不改变级别</t>
+          <t>全日制博士研究生无行政级别，LLM1判断正确。</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委</t>
+          <t>宁东能源化工基地党工委</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5240,46 +5252,46 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>自治区党委副书记为副部级，LLM1正确</t>
+          <t>宁东能源化工基地党工委为正厅级机构，书记常规级别正厅级，无高配标注时按机构级别定级。</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>宁东能源化工基地管委会</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5294,48 +5306,48 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>浙江省委副书记标准为副部级，LLM1判断正确；LLM2误判为正部级</t>
+          <t>宁东能源化工基地管委会为正厅级派出机构，其主任职务基准为正厅级，个人兼任副部级不改变职务本身级别。</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>宁东能源化工基地党工委</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>党工委书记、管委会主任</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -5343,51 +5355,51 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>浙江省委副书记常规为副部级，LLM2误判为正部级。</t>
+          <t>宁东基地党工委由自治区党委常委兼任，高配副部级，LLM2判断正确；LLM1按机构基准级别定为正厅级，但忽略了兼任高配。</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>浙江省政府</t>
+          <t>宁东能源化工基地管委会</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>副省长、代省长</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5406,27 +5418,27 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>浙江省代省长通常为正部级，与省长同级。兼任副省长不影响主职级别。</t>
+          <t>袁家军任宁东管委会主任时为宁夏回族自治区党委常委，个人行政级别为副部级，机构虽或为正厅但个人高配。</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共浙江省委政法委</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5436,12 +5448,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5456,48 +5468,48 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>浙江省委副书记属省部级副职，LLM1正确</t>
+          <t>省委政法委副书记通常为正厅级，专职副书记无常委等兼任时即为厅局级正职，LLM2误判为副部级。</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>第十三届全国人民代表大会监察和司法委员会</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>副书记、政法委书记</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -5505,21 +5517,21 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>全国人大专门委员会副主任委员标准为副部级，车俊虽曾任正部级但现职对应副部级</t>
+          <t>省委副书记为副部级，兼任政法委书记仍为副部级，非正部级。</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -5530,26 +5542,26 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>航空航天工业部第五研究院501部结构室</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>副主任</t>
+          <t>副书记、政法委书记</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>副科级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5559,79 +5571,75 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>单位层级不确定，仅'副主任'难以精确推断为副科级，符合早期经历难以判断规则</t>
+          <t>浙江省委副书记（非省长兼任）通常为副部级，政法委书记也为副部级，并无正部级依据。</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>袁家军</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>航天工业总公司第五研究院501部</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>副主任</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>副处级</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="B95" t="n">
+        <v>28</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>副书记、政法委书记</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>航天系统内设机构副主任通常对应副处级，LLM2判断更符合常规定级。</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="n">
+        <v>100</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>省委副书记（非省长）为副部级，任职单位中共浙江省委，无高配依据，LLM1误判为正部级。</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -5642,26 +5650,26 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>北京航空航天大学</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>博士研究生</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5676,16 +5684,16 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>博士研究生为全日制学习经历，无行政级别。</t>
+          <t>省委书记本为正部级，未提及政治局委员高配</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -5696,26 +5704,26 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>浙江省人大常委会</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5725,25 +5733,21 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
         <v>95</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>仅知中央党校进修学员，无班次及原职务信息，无法定级</t>
+          <t>浙江省人大常委会主任岗位法定级别为正部级，虽袁家军个人为政治局委员（副国级），但本题按职务单位判断级别，应以岗位定级为准。</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -5754,16 +5758,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共重庆市委</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>副书记、政法委书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5773,7 +5777,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5792,42 +5796,42 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>省委副书记（非省长）为副部级，正部级判断错误。</t>
+          <t>重庆为直辖市，市委书记通常由中央政治局委员兼任，为副国级，非正部级。</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>浙江省政府</t>
+          <t>厦门市政府</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>常务副省长</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5837,51 +5841,51 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>浙江省政府常务副省长按机构定级原则为副部级，非正部级。</t>
+          <t>厦门为副省级市，市政府副秘书长通常为副局级（对应正处级），LLM1判断正处级更准确。</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共厦门市湖里区委</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>副书记、政法委书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5891,7 +5895,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5900,42 +5904,42 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>浙江省委副书记（非省长兼任）为副部级，LLM2正确</t>
+          <t>厦门为副省级市，其市辖区为副厅级建制，区委副书记为副职，对应正处级。</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>厦门市政府</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>副书记、政法委书记</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5945,51 +5949,51 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>中共浙江省委副书记为副部级，LLM2判断正确</t>
+          <t>厦门为副省级市，市政府副秘书长对应正处级，非副厅级。</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>山东省单县李半庄乡团委</t>
+          <t>福建省发展和改革委员会</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副主任、党组副书记</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>正科级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5999,51 +6003,51 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>乡团委书记通常为股级或副科级，非正科级；信息不足以明确级别，应填难以判断。</t>
+          <t>省发改委为正厅级单位，副主任一般为副厅级，党组副书记不改变级别。LLM1判断正确。</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>山东省委党校</t>
+          <t>国家能源局</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>本科生</t>
+          <t>副局长、党组成员</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6062,27 +6066,27 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>党校本科生属于全日制学习经历，无行政级别，LLM2正处级无依据</t>
+          <t>国家能源局为副部级国家局，副局长应为正厅级。</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>中共菏泽市委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6092,12 +6096,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6107,51 +6111,51 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>地级市委副书记标准副厅级，LLM2错误</t>
+          <t>浙江省委副书记（非省长）属副部级，LLM2正确。</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>菏泽市政府</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>市长</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6161,21 +6165,21 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>菏泽市为地级市，市长正职为正厅级</t>
+          <t>省委副书记（非省长）通常为副部级，LLM2准确；LLM1误判为正部级。</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6186,11 +6190,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>中共菏泽市牡丹区委</t>
+          <t>山东省单县李半庄乡团委</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6200,12 +6204,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副科级</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6215,21 +6219,21 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>牡丹区是普通地级市菏泽市的区，区委书记标准为正处级，LLM2误以为副厅级。</t>
+          <t>乡团委书记可能无正式行政级别（股级）或高配为副科级，仅凭该条目无法确定，信息不足时宜判为“难以判断”</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6240,26 +6244,26 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>中共菏泽市牡丹区委</t>
+          <t>山东省委党校</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>本科生</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>正处级</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>副厅级</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6274,16 +6278,16 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>菏泽市为地级市，其区委书记标准级别为正处级，LLM1判断正确。</t>
+          <t>党校本科生为全日制学生，不具备行政级别，应填“无”，正处级无依据。</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6294,16 +6298,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>中共菏泽市牡丹区委党校</t>
+          <t>中共菏泽市牡丹区委</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>校长</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6323,25 +6327,21 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>正科级</t>
-        </is>
-      </c>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>区委党校为正科级单位，专职校长应为正科级，LLM1/2均明显偏高。</t>
+          <t>菏泽市为普通地级市，其市辖区区委书记标准为正处级，无常委等高配信息，故采纳LLM1。</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6352,11 +6352,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共菏泽市委</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6390,42 +6390,42 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>浙江省委副书记通常为副部级，LLM1判断正部级错误。</t>
+          <t>菏泽为普通地级市，市委副书记标准为副厅级，LLM2准确</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>易炼红</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>湖南省涟源县桂花公社</t>
+          <t>中共滨州市委</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>知青</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6435,51 +6435,51 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>知青为生产劳动经历，不属于正式工作职务，无行政级别</t>
+          <t>地级市市委副书记一般为副厅级，LLM2判断准确</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>易炼红</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>江西省政府</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>副省长、代省长、党组书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6494,16 +6494,16 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>代省长行使省长职权，级别为正部级；副省长为副部级，但代省长高配为正部级。</t>
+          <t>浙江省委副书记（不兼省长）常规为副部级，非正部级。</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6514,26 +6514,26 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>中共江西省委</t>
+          <t>湖南省涟源县桂花公社</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>知青</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6548,16 +6548,16 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>省委副书记是副部级，LLM1正确，LLM2错误</t>
+          <t>知青是不具备行政级别的特殊历史经历，属于明确的“无级别”，而非信息不足导致的“难以判断”。</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6568,26 +6568,26 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>中央纪委国家监委</t>
+          <t>中共湖南省委党校</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>接受纪律审查和监察调查</t>
+          <t>科技教研室副主任</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6597,21 +6597,21 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>该经历为调查事件，非职务任职，不具行政级别。</t>
+          <t>省委党校为正厅级，教研室处级，副主任定副处级准确，非难以判断。</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6622,16 +6622,16 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>湘潭钢铁公司第二炼钢厂转炉车间</t>
+          <t>湘潭钢铁公司第二炼钢厂</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>副主任</t>
+          <t>转炉车间副主任</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -6660,12 +6660,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>车间副主任在省属国企内部，无明显行政级别标注，信息不足以定级。</t>
+          <t>国企车间副主任通常对应副科级，信息足以定级，非难以判断。</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>湘潭钢铁公司第二炼钢厂转炉车间</t>
+          <t>湘潭钢铁公司第二炼钢厂</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>转炉车间主任</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6705,25 +6705,21 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="n">
         <v>80</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>湘潭钢铁公司车间主任无明确行政级别对应，信息不足</t>
+          <t>湘潭钢铁公司为省属国企，二级厂矿车间主任通常对应正科级职务，非模糊职务足以定级。</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6730,7 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
@@ -6772,12 +6768,12 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>湘潭钢铁集团为省属大型国企，二级分厂副厂长通常对应副处级，信息充分可定级。</t>
+          <t>湘潭钢铁集团为省属国企，二级分厂副厂长通常对应副处级，LLM1过度谨慎</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6784,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6826,12 +6822,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>湘潭钢铁集团为省属正厅级国企，其二级单位厂长通常为正处级，LLM2更准确。</t>
+          <t>省属国企二级厂厂长通常为正处级，非模糊职务，可推断。</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6838,7 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
@@ -6871,79 +6867,75 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>省属大型国企总经理助理常对应正处级，职务具体可推断级别</t>
+          <t>省属国企总经理助理级别因企业层级及岗位设置不同难以准确定级，信息不足，宜判定为难以判断。</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>刘捷</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="B119" t="n">
+        <v>8</v>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>湖南华菱管线股份有限公司湘钢事业部</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>总经理助理</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>正处级</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>省属国企二级单位总经理助理通常对应正处级，信息充分可推断</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>90</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>国企事业部总经理助理级别与企业架构挂钩，无通用级别映射，原文信息不足以定级，难以判断更稳妥。</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6946,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6963,7 +6955,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>硕士研究生</t>
+          <t>研究生</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6986,22 +6978,18 @@
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
         <v>100</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>硕士研究生学习经历一般无行政级别，LLM2判断错误</t>
+          <t>研究生为全日制学习，无行政级别</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7000,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -7050,174 +7038,178 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>省属国企总经理助理无明确级别对应，信息不足以定级。</t>
+          <t>国企总经理助理级别因企业级别不明确无法确定，LLM2将不确定情况定级为“正处级”过于武断。</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>刘捷</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>15</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>中国地质大学经济管理学院</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>博士研究生</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
+      <c r="B122" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>副总经理</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团为省属国企华菱集团子公司，未明确行政级别，副总经理可能为正处级或副厅级，信息不足以定级。</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>执行董事、总经理</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>省属国企级别需根据归口管理判断，原文未提供湘潭钢铁集团具体级别，无法确定正厅或副厅。</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>中国地质大学</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>研究生</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>正厅级</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="n">
-        <v>100</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>博士研究生为全日制学习经历，不具行政级别。</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>19</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>中共新余市委</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="n">
-        <v>95</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>新余市为地级市，市委副书记标准为副厅级，LLM1误判为正厅级。</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>38</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>浙江省政府</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>党组书记、副省长、代理省长</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="n">
-        <v>100</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>浙江省政府代理省长与正式省长同为正部级。LLM2判断正确。</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>deepseek-reasoner</t>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>两者均存疑</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>仅“研究生”无法判断全日制或在职，不足以定级；LLM1判“无”忽略保留原级可能，LLM2判“正厅级”无据，两者均错。</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -7228,11 +7220,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共省长株潭“两型社会”建设综合配套改革试验区工委</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7242,12 +7234,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7257,21 +7249,21 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>省委副书记是标准副部级职务，无任何信息支持正部级</t>
+          <t>长株潭试验区工委为正厅级机构，副书记一般为副厅级，未标明高配，LLM2判断更准确。</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>
@@ -7282,26 +7274,26 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>浙江省政府</t>
+          <t>中共新余市委</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>副省长、代省长</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7311,21 +7303,129 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>代省长与省长同级别，省长为正部级，LLM2正确。</t>
+          <t>地级市市委副书记（非市长）标准级别为副厅级，LLM2正厅级系混淆市长兼任情况。</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>deepseek-reasoner</t>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>33</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>95</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>省委副书记（非兼任省长）为副部级，LLM1误判为正部级。</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>35</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>95</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>浙江省委副书记不兼任省长时，通常为副部级，非正部级。</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
     </row>

--- a/output/浙江/浙江_battle3.xlsx
+++ b/output/浙江/浙江_battle3.xlsx
@@ -428,13 +428,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -523,17 +523,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>工作队组长、调研室组长、土改工作队中队长、办公室秘书、调研科科长</t>
+          <t>工作队组长、地委调研室组长、土改工作队中队长、地委办公室秘书、地委调研科科长</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>正科级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -548,128 +548,124 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>台州地委为正厅级，内设调研科科长为正科级，LLM2正确。</t>
+          <t>多职混杂跨度大，含秘书/组长，缺时间对应与机构级别线索</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>葛洪升</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>猫跳河六级电站指挥部</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>指挥、党委书记</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="B3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>电力工业部新安江工程局</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>党委办公室副主任、党委宣传部副部长、部长</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>工程局属厅局级单位，党委办副主任、宣传部长通常为处级</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>葛洪升</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>浙江省建委办公室</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>副主任</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>副厅级</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>85</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>猫跳河六级电站指挥部为临时性工程建设机构，原文仅提供职务而未说明机构隶属层级或对应行政级别，无法确定其正厅或副厅，信息不足定级。</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>葛洪升</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>浙江半山电厂指挥部</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>指挥、党委书记</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>半山电厂指挥部为省重点工程，指挥通常为副厅级；其前职系地厅级单位副职，平调为副厅级，后续升任正厅级省电力局局长，故副厅级更准确。</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>94</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>省建委属厅级，办公室副主任通常为副处级</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -680,26 +676,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>浙江省经委</t>
+          <t>浙江省计经委</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>副主任、党组副书记</t>
+          <t>办公室副主任</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>副厅级</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>正厅级</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -714,16 +710,16 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>浙江省经委为正厅级单位，副主任为副厅级，LLM1判断正确；LLM2误将副主任定为正厅级。</t>
+          <t>省计经委为正厅级，其办公室副主任通常副处级</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -734,26 +730,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>国务院特区办公室</t>
+          <t>水利电力部新安江工程局</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>副主任、党组副书记</t>
+          <t>党委宣传部部长</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -763,21 +759,21 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>葛洪升原为浙江省省长（正部级），调任国务院特区办副主任时明确为正部长级，实际为正部级。</t>
+          <t>工程局内设宣传部部长通常为处级，党委部门难高至副厅</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -788,26 +784,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>全国人大财经委员会</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>离职休养</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -817,99 +809,95 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>全国人大专门委员会副主任委员标准为副部级岗位，无明确正部长级标注时按基准定级，故LLM1更准确。</t>
+          <t>“离职休养”非职务且无前文承接，不能定级</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>葛洪升</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>中共中央委员会</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>十三届中央候补委员</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>万学远</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>中共上海交通大学210教研组党支部</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>书记</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>85</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>中央候补委员属于党内职务，本身不直接对应行政级别，且本条经历未提供同时担任的行政职务，无法推断具体级别。</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>正科级</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>高校教研组党支部属基层党支部，书记通常按科级把握</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中共中央委员会</t>
+          <t>东北丰满水力发电厂</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>十四届中央委员</t>
+          <t>学员</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -919,7 +907,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -929,45 +917,41 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>中央委员本身无固定行政级别，需结合当时具体职务判断，不能笼统判定为正部级或判定为无。</t>
+          <t>“学员”属学习培训身份，通常按无级别处理</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>葛洪升</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>全国人大常委会</t>
+          <t>浙江黄坛口水电厂</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>九届全国人大常委会委员</t>
+          <t>学员</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -977,7 +961,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -987,28 +971,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>全国人大常委会委员通常对应正部级，LLM1判断为“无”明显错误。</t>
+          <t>“学员”属学习培训身份，通常无行政级别</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1016,22 +1000,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海交通大学210教研组党支部</t>
+          <t>中央党校培训部</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>正科级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1046,23 +1030,23 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>高校教研组党支部书记多为兼职，无明确行政级别对应，无法用标准行政级别衡量，信息不足定级。</t>
+          <t>“进修学员”属学习经历，按规则应为无级别</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1070,22 +1054,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海市青年联合会</t>
+          <t>煤炭工业部干部管理学院</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>主席</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1095,53 +1079,53 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>上海市为直辖市，市青年联合会作为地方性人民团体一般为正厅级，主席为正厅级正职。</t>
+          <t>“进修学员”属学习经历，按规则应为无级别</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>人事部</t>
+          <t>中共浙江省纪委</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>副部长、党组副书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>副部级</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -1149,41 +1133,41 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>人事部为正部级国务院组成部门，副部长为副部级，党组副书记不改变行政级别。</t>
+          <t>省纪委属省级领导机关，副书记通常为副部级</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>国家外国专家局</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>局长、党组书记</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1193,7 +1177,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1203,51 +1187,55 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>国家外国专家局为人社部管理的副部级国家局，局长、党组书记应为副部级，LLM1判断正确，LLM2误作正部级。</t>
+          <t>仅知中央党校进修，未知班次与任前职务</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>万学远</t>
+          <t>柴松岳</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中国国际人才交流协会</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>副主席</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>副部级</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>正部级</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1262,16 +1250,16 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>万学远卸任国家外国专家局局长(明确正部长级)后任此职，保留正部级待遇，协会副主席按本人原级别定级。</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1282,26 +1270,26 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>东北丰满水力发电厂</t>
+          <t>全国政协</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>学员</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1316,16 +1304,16 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>学员非全日制学生,按早期模糊职务规则应填难以判断,LLM1误填为无</t>
+          <t>全国政协常委通常对应副部级政治地位</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1336,26 +1324,26 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>浙江黄坛口水电厂</t>
+          <t>全国政协经济委员会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>学员</t>
+          <t>副主任</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1370,41 +1358,41 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>电厂学员属岗前培训，非全日制学生，亦无职务级别，难以判断行政级别。</t>
+          <t>全国政协专门委员会副主任通常为副部级</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>柴松岳</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新安江水电运行分场</t>
+          <t>吉林省汪清县罗子沟公社太平大队</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>值班员、机械值班长、党支部书记</t>
+          <t>知青</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>正科级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1424,95 +1412,99 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>值班员、机械值班长等职务无明确级别对应，信息不足。</t>
+          <t>知青属社会身份非学生，非行政职务，级别信息不足</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>柴松岳</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>富春江水电厂</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>值班员、党支部书记、党委委员、揭批查办公室负责人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>张德江</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>吉林省汪清县革委会机关团支部</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>书记</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>90</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>富春江水电厂的企业级别不明，值班员、党支部书记等职务无法直接确定行政级别，信息不足以定级，故LLM2的“难以判断”更准确。</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>副科级</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>正科级</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>县革委会机关团支部书记通常对应科级单位正职</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>柴松岳</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>富春江水电厂</t>
+          <t>中共留学生党支部</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>党委常委、副书记、厂长、党委书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1532,70 +1524,74 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>富春江水电厂行政级别未知，虽有厂长/党委书记职务，但无法从原文确定其处级/厅级归属，属难以判断。</t>
+          <t>留学生党支部层级不明，书记级别无法确定</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>柴松岳</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>中共延吉市委</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>正处级</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>仅凭‘中央党校 进修学员’无法确定班次与级别，需结合前后职务推断；孤立条目应标‘难以判断’。</t>
+          <t>延吉为县级市，市委副书记通常正处级</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1606,26 +1602,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>朝鲜金日成综合大学经济系</t>
+          <t>中共延边州委</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1635,25 +1631,21 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>仅凭‘进修学员’无法判断是否在职进修或保留原级别，缺乏前后履历依据。</t>
+          <t>延边州属地级自治州，州委副书记通常为正厅级</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1656,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1673,41 +1665,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>正厅级</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>95</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>延边州为地级行政区，州委为正厅级单位，副书记常规为副厅级，LLM2判断准确。</t>
+          <t>延边州属副省级以下自治州，州委书记通常正厅级</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1718,26 +1714,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中共吉林省委</t>
+          <t>中共广东省委</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>正部级</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1752,16 +1748,16 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>省委专职副书记（非省长）标准级别为副部级，LLM2判断正确。LLM1误判为正部级。</t>
+          <t>省委书记属省部级正职，未见兼任更高职务</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1772,11 +1768,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中共延边州委</t>
+          <t>中共重庆市委</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1786,12 +1782,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1801,51 +1797,51 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>延边州为地级自治州，非副省级城市，其党委书记标配正厅级，除非明确省委常委兼任才会高配副部级，原文仅书记职务无高配信息，故正厅级更准确。</t>
+          <t>重庆市委书记职务本身属正部级，未给出兼任政治局常委信息</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>习近平</t>
+          <t>张德江</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>陕西省延川县文安驿公社梁家河大队</t>
+          <t>国务院</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>知青、党支部书记</t>
+          <t>副总理、党组成员</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>正科级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1860,16 +1856,16 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>大队党支部书记是村级职务，不纳入国家行政编制，无明确行政级别，符合'难以判断'规则。</t>
+          <t>国务院副总理属国家级副职，即副国级</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1880,16 +1876,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中共福州市委</t>
+          <t>厦门市政府</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副市长</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1899,7 +1895,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1909,21 +1905,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>福州市为地级市（非副省级市），市委书记标准级别为正厅级；未提省委常委兼任，不能默认高配副部级。</t>
+          <t>厦门系副省级市，副市长通常对应副厅级</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1934,26 +1930,26 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>福州市人大常委会</t>
+          <t>中共福州市委</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1968,16 +1964,16 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>福州市为普通地级市，非副省级市；福州市人大常委会主任为该市四大班子正职之一，职务本身为正厅级。</t>
+          <t>福州时为副省级市，市委书记通常副部级</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1988,21 +1984,21 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中共福州军分区党委</t>
+          <t>中共福建省委</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>党委第一书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2017,21 +2013,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>福州市为地级市，福州市委书记为正厅级，兼任军分区党委第一书记不提升级别。</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2042,26 +2038,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>中共福建省委</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2071,21 +2067,21 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>省委副书记为副部级，非省长兼任时无正部级依据。</t>
+          <t>中共中央政治局常委属正国级。</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2096,26 +2092,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>中共福建省委、中共福州市委</t>
+          <t>中共中央书记处</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>副书记、书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2130,16 +2126,16 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>福建省委副书记为副部级，兼任福州市委书记（正厅级），就高为副部级，非正部级。</t>
+          <t>中央书记处书记属党和国家副职序列，通常为副国级</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2150,26 +2146,26 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>福州市人大常委会</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,25 +2175,21 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>福州市为地级市，其人大常委会主任为正厅级，非副省级或正部级。</t>
+          <t>中共中央政治局常委属党和国家最高领导层，按标准为正国级</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2208,26 +2200,26 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>福州军分区</t>
+          <t>中共中央书记处</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>党委第一书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2237,25 +2229,21 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>仅凭“福州军分区党委第一书记”无法确定行政级别，两人判断均缺乏依据且明显错误。</t>
+          <t>中央书记处书记属党和国家副职层级，通常为副国级</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2266,26 +2254,26 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>中共福建省委</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2300,16 +2288,16 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>省委副书记一般为副部级，仅当兼任省长时为正部级，此处未注明兼任省长，故应为副部级</t>
+          <t>国家副主席属国家级副职，即副国级</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2320,26 +2308,26 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>福建省高炮预备役师</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>第一政委</t>
+          <t>校长</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2349,25 +2337,21 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>预备役师第一政委通常由地方领导兼任，级别不确定，无法从职务本身判断。</t>
+          <t>中央党校校长通常由政治局常委兼任，职务对应副国级</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2378,26 +2362,26 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>中共福建省委</t>
+          <t>中共中央政治局</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2407,21 +2391,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>单任省委副书记（未兼省长）为副部级，LLM1误判为正部级，LLM2判断正确。</t>
+          <t>中共中央政治局常委属正国级领导职务</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2432,28 +2416,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>中华人民共和国</t>
+          <t>中共中央书记处</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>副主席</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -2461,21 +2445,21 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>国家副主席法定级别为国家级副职（副国级），不因个人党内兼任而改变该职务的基准级别。</t>
+          <t>中央书记处书记属党和国家领导人，行政级别为副国级</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2500,14 +2484,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -2515,79 +2499,75 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>国家副主席职务基准为副国级；虽习近平当时高配正国级，但基于职务本身判断应取副国级。</t>
+          <t>国家副主席属国家副职，副国级。</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>习近平</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B39" t="n">
         <v>60</v>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>中共中央军事委员会</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>副主席</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>中央军委副主席可为副国级或正国级（政治局常委兼任），单凭职务无法确定个人级别，需看是否政治局常委。</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>98</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>中央军委副主席属国家级副职，对应副国级</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2612,14 +2592,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -2627,21 +2607,21 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>中央军委副主席职务法定为副国级，正国级须主席职务。</t>
+          <t>国家军委副主席属国家级副职，对应副国级</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2652,28 +2632,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>中华人民共和国</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>副主席</t>
+          <t>校长</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -2681,21 +2661,21 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>国家副主席职务本身为副国级，不考虑其兼任的其他更高职务。</t>
+          <t>中央党校校长通常由政治局常委兼任，职务对应副国级</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2706,11 +2686,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>中华人民共和国中央军事委员会</t>
+          <t>中华人民共和国</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2720,14 +2700,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>副国级</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>正国级</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -2735,51 +2715,51 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>中央军委副主席职务本身为副国级，不附加政治局常委等兼任信息时应按职务定级。</t>
+          <t>国家副主席属国家级副职，即副国级</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>吕祖善</t>
+          <t>习近平</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>全国人大财政经济委员会</t>
+          <t>中华人民共和国中央军事委员会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>副主席</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正国级</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2794,16 +2774,16 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>吕祖善曾任浙江省省长（正部级），转任全国人大财经委副主任委员后保留原级别，实际为正部级。</t>
+          <t>中央军委副主席属国家级副职，通常为副国级</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2814,26 +2794,26 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>第十二届全国人大常委会</t>
+          <t>南京航空学院</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>常委</t>
+          <t>留校待分配</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2848,16 +2828,16 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>全国人大常委会委员（常委）通常享受正部级政治、生活待遇，惯例按正部级对待。</t>
+          <t>“留校待分配”非正式职务，非在校学习，级别不足判定</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -2868,26 +2848,26 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>第十二届全国人大财政经济委员会</t>
+          <t>解放军部队农场</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>副主任委员</t>
+          <t>劳动锻炼</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2902,46 +2882,46 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>全国人大专门委员会副主任委员通常对应正部级，且吕祖善此前为浙江省省长（正部级），转任为平级调整。</t>
+          <t>劳动锻炼非学习，且无职务层级信息，宜难以判断</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>吕祖善</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>中共内蒙古自治区呼伦贝尔盟牧管局党委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>常委、政治部主任</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2951,51 +2931,51 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>牧管局级别不明，赵洪祝早期经历信息不足以确定具体级别，符合难以判断规则</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>吕祖善</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>中共内蒙古自治区扎兰屯牧场党委</t>
+          <t>全国人大财政经济委员会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>常委、副书记、纪委书记</t>
+          <t>副主任委员</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>副科级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3005,51 +2985,55 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
       <c r="J47" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>扎兰屯牧场级别不明确，无法准确推断，故难以判断更合理。</t>
+          <t>全国人大专门委员会副主任委员通常为副部级</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>赵洪祝</t>
+          <t>吕祖善</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>全国人大常委会</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3059,79 +3043,79 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>97</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>全国人大常委会委员长会议成员非必然；常委会组成人员属副国级序列</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>吕祖善</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>26</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>全国人大财政经济委员会</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>副主任委员</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>自行修正</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>90</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>仅凭“中央党校 进修学员”无法确定级别，需此前职务，信息不足。</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>赵洪祝</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>中共内蒙古自治区兴安盟委</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>委员</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>“中共兴安盟委 委员”未明确是否为常委，单独看无法确定级别，LLM1和LLM2均无充足依据。</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>96</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>全国人大专门委员会副主任委员通常为副部级</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -3142,26 +3126,26 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>中共内蒙古自治区兴安盟委</t>
+          <t>解放军总后勤部内蒙古扎兰屯军马场三连</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>委员、组织部部长</t>
+          <t>牧工</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3180,12 +3164,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>兴安盟是地级行政区，盟委委员为副厅级，组织部长由盟委委员兼任，确为副厅级</t>
+          <t>牧工属工作经历非学生，军马场三连无法据此定级</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -3196,16 +3180,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>中央党校</t>
+          <t>解放军总后勤部内蒙古扎兰屯军马场卫生院</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>职工</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3215,7 +3199,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3225,163 +3209,159 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>95</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>“职工”非学生，且无法据单位职工身份定行政级别</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>赵洪祝</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古自治区呼伦贝尔盟牧管局</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>党委常委、政治部主任</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="J51" t="n">
-        <v>90</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>仅“进修学员”无上下文，无法确定原级别，不符合“无”也不可妄定副厅，应判难以判断</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>夏宝龙</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>中共浙江省委</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>95</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>浙江省委副书记（非省长兼任）一般为专职副书记，属副部级。</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>盟属局一般处级，党委常委兼政治部主任通常副职</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>夏宝龙</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>29</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>中共浙江省委</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>95</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>省委副书记（不兼省长）标准级别为副部级，LLM2正确。</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>赵洪祝</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>中共内蒙古自治区扎兰屯牧场委员会</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>常委、副书记、纪委书记</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>牧场党委属县处级单位，副书记、纪委书记通常副处级</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>中共浙江省委政法委员会</t>
+          <t>中共内蒙古自治区兴安盟委组织部</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>干部科科长</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3396,46 +3376,46 @@
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>浙江省委政法委书记通常由省委常委兼任，省委常委为副部级，该职务并非正部级。LLM1判断有误。</t>
+          <t>盟委组织部为正处级部门，内设干部科科长通常正科级</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>浙江省社会治安综合治理委员会</t>
+          <t>中共内蒙古自治区兴安盟盟委</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>委员</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3450,46 +3430,46 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>省级综治委主任通常由省委副书记兼任，为副部级，非正部级。</t>
+          <t>盟委委员属地委常委层级，兴安盟为地级，通常正处级</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3499,51 +3479,55 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J56" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>省委副书记（非省长）为副部级</t>
+          <t>仅知中央党校进修，缺班次与前后职务，无法定级</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>夏宝龙</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共内蒙古自治区兴安盟盟委</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>委员</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3558,46 +3542,46 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>省委副书记通常为副部级，除非兼任省长才为正部级，此处仅副书记无兼任信息，应为副部级。</t>
+          <t>盟委委员属地级党委班子成员，通常为正处级</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>浙江省瑞安县莘塍区团委</t>
+          <t>中共内蒙古自治区兴安盟盟委组织部</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>部长</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>正科级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3607,51 +3591,51 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>县辖区团委负责人职务模糊，单位层级不足以确定正科级，信息不足宜判断为难以判断。</t>
+          <t>盟委组织部长通常兼盟委委员，按地级班子副职多为副厅级</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>浙江省民政厅</t>
+          <t>中央纪律检查委员会</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>党组成员、人事处处长</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3666,46 +3650,46 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>省民政厅为正厅级单位，内设人事处为正处级，处长为正处级，党组成员不改变行政级别，仍为正处级。</t>
+          <t>中纪委副秘书长一般为内设机构副职，通常正厅级</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>中共永康市委</t>
+          <t>中央纪律检查委员会办公厅</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3715,51 +3699,51 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>永康为县级市，市委书记常规为正处级。无高配信息时，LLM1判断更准确。</t>
+          <t>中纪委办公厅属内设厅局，办公厅主任通常为正厅级</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>赵洪祝</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>浙江大学研究生课程进修班</t>
+          <t>中共中央纪律检查委员会</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>研究生</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3769,45 +3753,41 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>研究生课程进修班为学习经历，无法从该条推断行政级别，需结合前后职务确定是脱产(无)还是在职保留级别。</t>
+          <t>中纪委常委通常按副部级掌握，非副书记非常务正部</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>永康市人大常委会</t>
+          <t>天津市河西区职工大学</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>在职学习</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3817,7 +3797,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3827,51 +3807,55 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J62" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>永康为普通县级市，四套班子正职为正处级，人大常委会主任为正处级，非副厅级。</t>
+          <t>在职学习非任职，原文无保留职级信息</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>天津市河西区政府</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>秘书长</t>
+          <t>副区长</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3881,51 +3865,51 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>省委秘书长通常由省委常委兼任，省委常委为副部级，故应采纳LLM1的副部级判断。</t>
+          <t>河西区属天津市辖区，副区长通常为副处级</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共天津市河西区委</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3935,46 +3919,46 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>浙江省委副书记通常为副部级，未注明正部长级，故LLM1判断准确。</t>
+          <t>市辖区区委常委通常对应副处级，河西区为正厅级直辖市辖区</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>安徽省合肥市中级人民法院</t>
+          <t>天津市河西区政府</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>助理审判员、审判员、办公室秘书、副主任、刑一庭副庭长、庭长、院党组成员</t>
+          <t>副区长</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3994,46 +3978,46 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>合肥市中级法院为副厅级，庭长通常为副处级，院党组成员亦对应副处级，LLM2判断正确。</t>
+          <t>天津市区政府属厅局级，副区长通常为副厅级以下正处级/副处级？河西区为市辖区，副区长一般副处级</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>华东政法学院</t>
+          <t>中共天津市河西区委</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>进修学员</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4043,50 +4027,46 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>仅凭进修学员无法确定级别，需上下文。LLM1误判为无，LLM2可能基于先验知识。</t>
+          <t>天津市河西区为市辖区，区委副书记通常为正处级</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>安徽省合肥市公安局</t>
+          <t>天津市河西区政府</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>局长、党委副书记、书记</t>
+          <t>区长</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4101,41 +4081,41 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>合肥市为普通地级市，其公安局为正处级单位，局长除非明确由副市长兼任，否则默认为正处级，LLM2正确。</t>
+          <t>天津为直辖市，市辖区区长通常为正厅级</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>中共合肥市委</t>
+          <t>中共天津市河西区委</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4145,7 +4125,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4155,41 +4135,41 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>合肥市为地级市，正厅级架构；市委副书记应为副厅级，正厅级通常为市委书记/市长。</t>
+          <t>天津市辖区区委书记，直辖市市辖区通常为正厅级</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>中共合肥市委</t>
+          <t>天津市河西区政府</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>区长</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4199,7 +4179,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4209,99 +4189,99 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>合肥为普通地级市，正厅级建制，市委副书记（非市长兼任）常规为副厅级，LLM2正确。</t>
+          <t>天津为直辖市，河西区属市辖区，区长通常正厅级</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>车俊</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>中央党校函授学院</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>夏宝龙</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>17</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>中央党校</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>进修学员</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>难以判断</t>
         </is>
       </c>
-      <c r="J70" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>仅凭'中央党校函授学院进修学员'无法确定其当时所任职务，无法推断行政级别；LLM1误判为无，LLM2无依据猜测副厅级，均不准确。</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="J70" t="n">
+        <v>94</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>仅知中央党校进修，未给班次与前后职务，无法定级</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>中共合肥市委</t>
+          <t>天津市委党校</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>研究生班在职学习</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4311,7 +4291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4321,36 +4301,40 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J71" t="n">
         <v>95</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>合肥是普通地级市，市委副书记通常为副厅级，LLM2判断正确，LLM1误认为正厅级</t>
+          <t>在职学习非任职，原文无保留职级信息</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>夏宝龙</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>中共河北省委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4380,46 +4364,46 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>专职省委副书记为副部级，无兼任省长等正部级职务，LLM2判断正确</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>中共河北省委</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>进修学员</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4429,51 +4413,55 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>自行修正</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
       <c r="J73" t="n">
         <v>95</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>省委副书记（非省长）通常为副部级，LLM2判断正确。</t>
+          <t>仅知进修学员，非任职；无在职保留级别线索</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>中共石家庄市委</t>
+          <t>中央党校</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>研究生</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4483,55 +4471,51 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>自行修正</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>石家庄为地级市，中共石家庄市委为正厅级机构，书记为正职，无省委常委等明确高配信息，故应为正厅级。LLM1正部级明显错误，LLM2副部级属于无依据高配。</t>
+          <t>研究生属学习经历，通常无行政级别</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委；中共新疆生产建设兵团委员会</t>
+          <t>香港理工大学管理学院</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>副书记；党委书记、政委</t>
+          <t>硕士研究生</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4541,53 +4525,53 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>新疆兵团为正省部级单位，党委书记、政委为正部级；LLM2仅看自治区党委副书记定级副部级，忽略兵团主官高配属实。</t>
+          <t>硕士研究生属学习经历，不具行政级别</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>需拆分提取：新疆生产建设兵团和中国新建集团公司</t>
+          <t>中共江苏省委</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>需拆分提取：党委书记、政委和董事长</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4595,53 +4579,53 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团为正部级建制，党委书记兼政委通常为正部级</t>
+          <t>江苏省委书记属省部级正职，未示兼任政治局常委</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>中国新建集团公司</t>
+          <t>江苏省人大常委会</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4649,53 +4633,53 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>中国新建集团公司为新疆生产建设兵团企业化名称，兵团政委兼董事长为正部级建制，车俊任该职时确为正部级。</t>
+          <t>省人大常委会主任属省级正职，通常正部级</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委、中共新疆生产建设兵团委员会</t>
+          <t>中共上海市委</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>副书记、党委书记、政委</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>副国级</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4703,53 +4687,53 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团为正省级单位，政委为正部级；兼任自治区党委副书记不影响主职级别，LLM1判断更准确。</t>
+          <t>仅据‘上海市委书记’职务本身属正部级，未示政治局委员</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>车俊</t>
+          <t>李强</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团</t>
+          <t>中共上海市委</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>党委书记、政委</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>正国级</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4757,21 +4741,21 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团为正省级建制，党委书记、政委为正部长级，LLM1正确。</t>
+          <t>上海市委书记职务本身属正部级，未给出兼政治局常委信息</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -4782,26 +4766,26 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>中国新建集团公司</t>
+          <t>安徽省长丰县东方红公社</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>董事长</t>
+          <t>知青</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4811,75 +4795,75 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>新疆生产建设兵团对外称中国新建集团公司，兵团政委兼任董事长，通常明确为正部长级（高配），车俊任期内即为正部级。</t>
+          <t>知青属身份非学生，公社经历无法对应明确行政级别</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>车俊</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>34</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>中央新疆工作协调小组</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>成员</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="B81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>安徽省长丰县东方红公社</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>团委副书记</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>副科级</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="n">
-        <v>90</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>车俊时任新疆生产建设兵团政委（正部级），中央新疆工作协调小组为其兼职，级别依主职定正部级。</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>公社团委属乡科级单位，副书记通常为副科级</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -4890,26 +4874,26 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>中共新疆维吾尔自治区委</t>
+          <t>中共安徽省长丰县三和公社委员会</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4919,7 +4903,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4928,12 +4912,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>省委副书记（非省长）标准为副部级</t>
+          <t>公社党委属乡科级，党委书记通常为正科级</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -4944,11 +4928,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共安徽省长丰县杨公区委</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4958,12 +4942,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4973,21 +4957,21 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>省委副书记（非省长）通常为副部级，LLM1判正部级无依据。</t>
+          <t>区委副书记属县辖区公所体系，通常为乡科级副职高配正科</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -4998,26 +4982,26 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>安徽省合肥市中级人民法院</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>助理审判员、审判员、办公室秘书、副主任、刑一庭副庭长、庭长、院党组成员</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正科级</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5032,36 +5016,36 @@
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>省委副书记（未兼任省长）为副部级，非正部级，LLM2判断正确。</t>
+          <t>地级市中院为正处级单位，庭长、党组成员通常正处</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>航空航天工业部五院501部结构室</t>
+          <t>安徽省合肥市中级人民法院</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>副主任</t>
+          <t>副院长、党组副书记</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5071,7 +5055,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>副科级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5086,99 +5070,95 @@
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>航空航天工业部五院（中国空间技术研究院）为正局级，其501部（总体部）为正处级，下设结构室为科级，副主任为副科级。</t>
+          <t>地级市中院通常正处高配，副院长多为副厅级</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>袁家军</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>中国航天工业总公司五院</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>院长助理、神舟一号飞船系统常务副总指挥</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>正处级</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>车俊</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>9</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>安徽省合肥市公安局</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>副局长、党委副书记</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>副厅级</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>航天工业总公司五院为厅级单位,院长助理级别通常在正处与副厅间,原文无足够信息定级,故难以判断</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>95</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>合肥为省会地级市，市公安局通常正处高配，副局长多为副厅</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>北京航空航天大学</t>
+          <t>安徽省合肥市公安局</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>博士研究生</t>
+          <t>局长、党委副书记、书记</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5193,51 +5173,51 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>全日制博士研究生无行政级别，LLM1判断正确。</t>
+          <t>合肥为省会地级市，市公安局局长通常副市级，兼书记就高按正厅</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>宁东能源化工基地党工委</t>
+          <t>中共合肥市委</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5252,46 +5232,46 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>宁东能源化工基地党工委为正厅级机构，书记常规级别正厅级，无高配标注时按机构级别定级。</t>
+          <t>合肥为地级省会，市委副书记通常为副厅级</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>宁东能源化工基地管委会</t>
+          <t>中共合肥市委</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5306,48 +5286,48 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>宁东能源化工基地管委会为正厅级派出机构，其主任职务基准为正厅级，个人兼任副部级不改变职务本身级别。</t>
+          <t>合肥为地级市，市委副书记通常为副厅级</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>宁东能源化工基地党工委</t>
+          <t>合肥市政府</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>党工委书记、管委会主任</t>
+          <t>常务副市长</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>正厅级</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -5355,51 +5335,51 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>宁东基地党工委由自治区党委常委兼任，高配副部级，LLM2判断正确；LLM1按机构基准级别定为正厅级，但忽略了兼任高配。</t>
+          <t>合肥为地级省会，常务副市长通常属副厅级</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>宁东能源化工基地管委会</t>
+          <t>中央党校函授学院</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>主任</t>
+          <t>函授学员</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5414,31 +5394,31 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>袁家军任宁东管委会主任时为宁夏回族自治区党委常委，个人行政级别为副部级，机构虽或为正厅但个人高配。</t>
+          <t>函授属在职学习，保留原级别，不按学生“无”</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>中共浙江省委政法委</t>
+          <t>中共合肥市委</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5448,12 +5428,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5468,41 +5448,41 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>省委政法委副书记通常为正厅级，专职副书记无常委等兼任时即为厅局级正职，LLM2误判为副部级。</t>
+          <t>地级市市委副书记通常为副厅级，合肥当时非副省级市</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共合肥市委</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>副书记、政法委书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5517,51 +5497,51 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>省委副书记为副部级，兼任政法委书记仍为副部级，非正部级。</t>
+          <t>合肥为副省级市，市委书记通常为正厅级</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>新疆生产建设兵团</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>副书记、政法委书记</t>
+          <t>党委书记、政委</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>正部级</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>副部级</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5576,77 +5556,77 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>浙江省委副书记（非省长兼任）通常为副部级，政法委书记也为副部级，并无正部级依据。</t>
+          <t>新疆生产建设兵团党委书记、政委通常为正部级岗位</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>袁家军</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>28</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>中共浙江省委</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>副书记、政法委书记</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>车俊</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>中国新建集团公司</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>董事长</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="n">
-        <v>100</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>省委副书记（非省长）为副部级，任职单位中共浙江省委，无高配依据，LLM1误判为正部级。</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>中国新建集团公司属央企，董事长通常副部级</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5654,24 +5634,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>新疆生产建设兵团</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>党委书记、政委</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -5679,95 +5659,95 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>省委书记本为正部级，未提及政治局委员高配</t>
+          <t>新疆生产建设兵团为省部级单位，党委书记、政委属正职</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>袁家军</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>车俊</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>浙江省人大常委会</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>主任</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>中国新建集团公司</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>董事长</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>副国级</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>采纳LLM1</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="n">
-        <v>95</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>浙江省人大常委会主任岗位法定级别为正部级，虽袁家军个人为政治局委员（副国级），但本题按职务单位判断级别，应以岗位定级为准。</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>中国新建集团为副部级央企，董事长通常副部级</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>袁家军</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>中共重庆市委</t>
+          <t>中共浙江省委</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5777,7 +5757,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>副国级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5792,46 +5772,46 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>重庆为直辖市，市委书记通常由中央政治局委员兼任，为副国级，非正部级。</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>厦门市政府</t>
+          <t>全国人大监察和司法委员会</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>副主任委员</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5846,46 +5826,46 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>厦门为副省级市，市政府副秘书长通常为副局级（对应正处级），LLM1判断正处级更准确。</t>
+          <t>全国人大专门委员会副主任委员通常为副部级</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>中共厦门市湖里区委</t>
+          <t>全国政协人口资源环境委员会</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>常委</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5904,42 +5884,42 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>厦门为副省级市，其市辖区为副厅级建制，区委副书记为副职，对应正处级。</t>
+          <t>全国政协专委会常委非政协常委会常委，通常副部级</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>车俊</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>厦门市政府</t>
+          <t>全国政协人口资源环境委员会</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>副秘书长</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副国级</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5954,46 +5934,46 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>厦门为副省级市，市政府副秘书长对应正处级，非副厅级。</t>
+          <t>全国政协专门委员会主任通常为正部级，非当然副国级</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>福建省发展和改革委员会</t>
+          <t>航空航天工业部五院501部</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>副主任、党组副书记</t>
+          <t>副主任</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6003,51 +5983,51 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>省发改委为正厅级单位，副主任一般为副厅级，党组副书记不改变级别。LLM1判断正确。</t>
+          <t>仅知‘501部副主任’，单位内设层级不明，难定级</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>国家能源局</t>
+          <t>航天工业总公司第五研究院第五〇一部</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>副局长、党组成员</t>
+          <t>副主任</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副处级</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>副部级</t>
+          <t>难以判断</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6057,100 +6037,100 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>国家能源局为副部级国家局，副局长应为正厅级。</t>
+          <t>仅知‘某部副主任’，内部层级不明，难准确定级</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>郑栅洁</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>20</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>中共浙江省委</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>正部级</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="n">
-        <v>90</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>浙江省委副书记（非省长）属副部级，LLM2正确。</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>袁家军</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>中国航天工业总公司五院</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>院长助理、神舟一号飞船系统常务副总指挥</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>五院为央企/部属科研单位，院长助理通常低于院长，副厅更稳妥</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>郑栅洁</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>宁东能源化工基地管委会</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>正部级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6165,51 +6145,51 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>省委副书记（非省长）通常为副部级，LLM2准确；LLM1误判为正部级。</t>
+          <t>宁东基地管委会通常为自治区派出机构，主任多为厅级</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>山东省单县李半庄乡团委</t>
+          <t>宁东能源化工基地管委会</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>主任</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>副科级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6219,51 +6199,51 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>乡团委书记可能无正式行政级别（股级）或高配为副科级，仅凭该条目无法确定，信息不足时宜判为“难以判断”</t>
+          <t>宁东基地管委会属宁夏自治区派出管理机构，主任通常为正厅级</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>山东省委党校</t>
+          <t>浙江行政学院</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>本科生</t>
+          <t>院长</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6273,51 +6253,51 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>党校本科生为全日制学生，不具备行政级别，应填“无”，正处级无依据。</t>
+          <t>浙江行政学院一般为省政府直属事业单位，院长通常正厅级</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>中共菏泽市牡丹区委</t>
+          <t>中共浙江省委政法委</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>书记</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6332,46 +6312,46 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>菏泽市为普通地级市，其市辖区区委书记标准为正处级，无常委等高配信息，故采纳LLM1。</t>
+          <t>省委政法委属正厅级部门，副书记通常为副厅或正厅，非副部</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>中共菏泽市委</t>
+          <t>浙江省政府</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>代省长、党组书记</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6386,46 +6366,46 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>菏泽为普通地级市，市委副书记标准为副厅级，LLM2准确</t>
+          <t>省政府代省长属省级政府正职，正部级</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>中共滨州市委</t>
+          <t>中共浙江省委政法委</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>正厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>正部级</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6435,32 +6415,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>地级市市委副书记一般为副厅级，LLM2判断准确</t>
+          <t>省委政法委书记通常为省委常委兼任，属副部级</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>袁家军</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -6474,14 +6454,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>正部级</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>副部级</t>
-        </is>
-      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -6489,51 +6469,51 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>浙江省委副书记（不兼省长）常规为副部级，非正部级。</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>易炼红</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>湖南省涟源县桂花公社</t>
+          <t>中共厦门市湖里区委</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>知青</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6548,46 +6528,46 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>知青是不具备行政级别的特殊历史经历，属于明确的“无级别”，而非信息不足导致的“难以判断”。</t>
+          <t>厦门系副省级市，市辖区区委副书记通常为正处级</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>易炼红</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>中共湖南省委党校</t>
+          <t>厦门市湖里区政府</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>科技教研室副主任</t>
+          <t>副区长</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>副处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6597,51 +6577,51 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>省委党校为正厅级，教研室处级，副主任定副处级准确，非难以判断。</t>
+          <t>厦门属副省级市，市辖区副区长通常为正处级</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>郑栅洁</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>湘潭钢铁公司第二炼钢厂</t>
+          <t>中共厦门市湖里区委</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>转炉车间副主任</t>
+          <t>副书记</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正处级</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>副科级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6651,154 +6631,154 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>采纳LLM2</t>
+          <t>采纳LLM1</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>国企车间副主任通常对应副科级，信息足以定级，非难以判断。</t>
+          <t>厦门为副省级市，市辖区区委副书记通常为正处级</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁公司第二炼钢厂</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>转炉车间主任</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>正科级</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁公司为省属国企，二级厂矿车间主任通常对应正科级职务，非模糊职务足以定级。</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>郑栅洁</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>17</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>国家能源局</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>副局长、党组成员</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>95</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>国家能源局属副部级国家局，副局长通常为正厅级</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁集团有限公司第二炼钢厂</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>副厂长</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>王浩</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>11</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>山东省菏泽地区体委</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>副处级</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM2</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁集团为省属国企，二级分厂副厂长通常对应副处级，LLM1过度谨慎</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>89</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>地区属地级，体委为地区政府工作部门，主任通常正处级</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>湘潭钢铁集团有限公司第二炼钢厂</t>
+          <t>中共山东省菏泽市牡丹区委员会</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>厂长</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6818,95 +6798,95 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>省属国企二级厂厂长通常为正处级，非模糊职务，可推断。</t>
+          <t>牡丹区属市辖区，区委书记通常为正处级</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁集团有限公司</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>总经理助理、第二炼钢厂厂长</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>王浩</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>19</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>中共菏泽市牡丹区委</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>书记</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>正处级</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>省属国企总经理助理级别因企业层级及岗位设置不同难以准确定级，信息不足，宜判定为难以判断。</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>95</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>菏泽市辖区区委书记，普通地级市市辖区主官通常正处级</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>湖南华菱管线股份有限公司湘钢事业部</t>
+          <t>中共菏泽市牡丹区委党校</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>总经理助理</t>
+          <t>校长</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6921,51 +6901,51 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>国企事业部总经理助理级别与企业架构挂钩，无通用级别映射，原文信息不足以定级，难以判断更稳妥。</t>
+          <t>区委党校属市辖区正处级单位，校长通常正处级</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>武汉科技大学</t>
+          <t>中共山东省委</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>研究生</t>
+          <t>副秘书长</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副厅级</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6980,46 +6960,46 @@
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>研究生为全日制学习，无行政级别</t>
+          <t>省委副秘书长通常为正厅级，属省党委办公厅厅级副职高配</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>湘潭钢铁集团有限公司</t>
+          <t>中共山东省淄博市委员会</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>总经理助理</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>难以判断</t>
+          <t>正厅级</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>正处级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7034,261 +7014,257 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>国企总经理助理级别因企业级别不明确无法确定，LLM2将不确定情况定级为“正处级”过于武断。</t>
+          <t>淄博为地级市，市委书记通常为正厅级。</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁集团有限公司</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>副总经理</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>王浩</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>32</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>山东省淄博市人大常委会</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>98</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>地级市人大常委会主任通常为正厅级，非副部级</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>王浩</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>33</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>中共山东省烟台市委员会</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>书记</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>98</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>烟台为地级市，市委书记通常为正厅级</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>王浩</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>41</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>浙江省政府</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>党组书记、副省长、代理省长</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>98</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>代理省长视同省长，浙江省长属正部级</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>易炼红</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>中共湖南省委党校</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>校长助理</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>副厅级</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁集团为省属国企华菱集团子公司，未明确行政级别，副总经理可能为正处级或副厅级，信息不足以定级。</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>湘潭钢铁集团有限公司</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>执行董事、总经理</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>采纳LLM1</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>省属国企级别需根据归口管理判断，原文未提供湘潭钢铁集团具体级别，无法确定正厅或副厅。</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>中国地质大学</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>研究生</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>两者均存疑</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>难以判断</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>仅“研究生”无法判断全日制或在职，不足以定级；LLM1判“无”忽略保留原级可能，LLM2判“正厅级”无据，两者均错。</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>刘捷</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>16</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>中共省长株潭“两型社会”建设综合配套改革试验区工委</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>副书记</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>正厅级</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>副厅级</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>采纳LLM2</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="n">
-        <v>85</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>长株潭试验区工委为正厅级机构，副书记一般为副厅级，未标明高配，LLM2判断更准确。</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro</t>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>省委党校一般为正厅级，校长助理通常按校级助理参照副厅</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>易炼红</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>中共新余市委</t>
+          <t>中共岳阳市委</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>书记</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>副厅级</t>
+          <t>副部级</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7303,41 +7279,41 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>采纳LLM1</t>
+          <t>采纳LLM2</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>地级市市委副书记（非市长）标准级别为副厅级，LLM2正厅级系混淆市长兼任情况。</t>
+          <t>岳阳为地级市，市委书记通常为正厅级</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>易炼红</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>江西省政府</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>副书记</t>
+          <t>副省长、代省长、党组书记</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7362,31 +7338,31 @@
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>省委副书记（非兼任省长）为副部级，LLM1误判为正部级。</t>
+          <t>江西副省长、代省长属省政府副职至正职过渡，代省长为副部级</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>刘捷</t>
+          <t>易炼红</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>中共浙江省委</t>
+          <t>中共江西省委</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7416,16 +7392,1042 @@
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>浙江省委副书记不兼任省长时，通常为副部级，非正部级。</t>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>5</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>湘潭钢铁公司第二炼钢厂转炉车间</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>副主任</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>副科级</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>88</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>仅知厂车间副主任，企业与车间规格不明，难定级</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>6</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>湘潭钢铁公司第二炼钢厂转炉车间</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>正科级</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>91</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>国企车间主任非党政职级，企业定级信息不足</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司第二炼钢厂</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>副厂长</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>副处级</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>大型省属钢企下属厂副职通常对应副处级</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司第二炼钢厂</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>厂长</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>大型省属钢企下属厂长通常为处级，信息足以推正处</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>总经理助理、第二炼钢厂厂长</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>大型省属钢企厂长通常为处级，总经理助理多不低于处级</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>湖南华菱管线股份有限公司湘钢事业部</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>总经理助理</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="n">
+        <v>89</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>企业内设职务“总经理助理”缺机构定级，难定对应行政级别</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>11</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>武汉科技大学</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>研究生</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>96</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>研究生属全日制学习经历，通常无行政级别</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>12</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>总经理助理</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>正处级</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>86</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>仅凭总经理助理及单位，缺少当时管理体制与高配信息</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>副总经理</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>湘钢属湖南省属大型国企，副总经理通常对应副厅级</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>湘潭钢铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>执行董事、总经理</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>难以判断</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>湘钢集团属大型省属国企，总经理通常正厅级</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>15</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>中国地质大学经济管理学院</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>博士研究生</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>99</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>博士研究生属学习经历，按规则行政级别为无</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>中共湖南省长株潭“两型社会”建设综合配套改革试验区工作委员会</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>省级工委副书记通常对应正厅，试验区工委规格较高</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>19</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>中共新余市委</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>96</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>地级市市委副书记通常为副厅级，未见兼市长信息</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>20</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>新余市政府</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>副市长、代市长</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>96</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>新余为地级市，代市长视同市长，属正厅级</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>21</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>中共新余市委</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>96</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>地级市市委副书记通常为副厅级，非市长不高配</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>24</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>中共江西省委</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>副秘书长</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>正厅级</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>副厅级</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>90</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>省委副秘书长通常对应副厅，江西省委副秘书长多为正厅配备</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>38</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>浙江省政府</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>党组书记、副省长、代理省长</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>96</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>代理省长视同省长，浙江省长属正部级</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>39</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>中共浙江省委</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>副书记</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>采纳LLM2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>97</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>省委副书记属省级党委副职，通常为副部级</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>刘捷</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>41</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>浙江省政府</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>副省长、代省长</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>正部级</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>副部级</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>采纳LLM1</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>96</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>省政府代省长视同省长，属正部级</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
